--- a/entregable/turno-de-madrugada-gestion.xlsx
+++ b/entregable/turno-de-madrugada-gestion.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="160">
   <si>
     <t>El turno de la madrugada</t>
   </si>
@@ -220,45 +220,36 @@
     <t>Salidas de mas de cinco horas</t>
   </si>
   <si>
-    <t>Tramites</t>
-  </si>
-  <si>
-    <t>Impresiones y radicacion de derechos de peticion</t>
+    <t>Publicacion</t>
+  </si>
+  <si>
+    <t>Dominio propio: prorrateo del periodo</t>
+  </si>
+  <si>
+    <t>Anualidad de 90.000 repartida</t>
+  </si>
+  <si>
+    <t>Alojamiento web y base de datos</t>
+  </si>
+  <si>
+    <t>Vercel y Supabase en plan gratuito</t>
+  </si>
+  <si>
+    <t>Distribucion del podcast</t>
+  </si>
+  <si>
+    <t>Spotify for Creators, sin costo</t>
+  </si>
+  <si>
+    <t>Postproduccion</t>
+  </si>
+  <si>
+    <t>Software de edicion de audio</t>
   </si>
   <si>
     <t>global</t>
   </si>
   <si>
-    <t>Solicitud a Bienestar Universitario</t>
-  </si>
-  <si>
-    <t>Publicacion</t>
-  </si>
-  <si>
-    <t>Dominio propio: prorrateo del periodo</t>
-  </si>
-  <si>
-    <t>Anualidad de 90.000 repartida</t>
-  </si>
-  <si>
-    <t>Alojamiento web y base de datos</t>
-  </si>
-  <si>
-    <t>Vercel y Supabase en plan gratuito</t>
-  </si>
-  <si>
-    <t>Distribucion del podcast</t>
-  </si>
-  <si>
-    <t>Spotify for Creators, sin costo</t>
-  </si>
-  <si>
-    <t>Postproduccion</t>
-  </si>
-  <si>
-    <t>Software de edicion de audio</t>
-  </si>
-  <si>
     <t>Audacity, software libre</t>
   </si>
   <si>
@@ -317,9 +308,6 @@
   </si>
   <si>
     <t>Verificacion factica de cada cifra</t>
-  </si>
-  <si>
-    <t>Redaccion y radicacion del derecho de peticion</t>
   </si>
   <si>
     <t>Produccion Nodo 1</t>
@@ -1270,7 +1258,7 @@
         <v>18</v>
       </c>
       <c r="B14" s="7">
-        <f>'1. Presupuesto'!G22</f>
+        <f>'1. Presupuesto'!G21</f>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -1278,7 +1266,7 @@
         <v>19</v>
       </c>
       <c r="B15" s="7">
-        <f>'1. Presupuesto'!G24</f>
+        <f>'1. Presupuesto'!G23</f>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -1286,7 +1274,7 @@
         <v>20</v>
       </c>
       <c r="B16" s="9">
-        <f>'2. Cronograma'!E17-'2. Cronograma'!D5+1</f>
+        <f>'2. Cronograma'!E16-'2. Cronograma'!D5+1</f>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -1337,7 +1325,7 @@
     <tabColor rgb="FF0EA5E9"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1680,19 +1668,19 @@
         <v>69</v>
       </c>
       <c r="D17" s="21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E17" s="20" t="s">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="F17" s="22">
-        <v>25000</v>
+        <v>7500</v>
       </c>
       <c r="G17" s="22">
         <f>D17*F17</f>
       </c>
       <c r="H17" s="23" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -1700,10 +1688,10 @@
         <v>54</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D18" s="16">
         <v>2</v>
@@ -1712,13 +1700,13 @@
         <v>51</v>
       </c>
       <c r="F18" s="17">
-        <v>7500</v>
+        <v>0</v>
       </c>
       <c r="G18" s="17">
         <f>D18*F18</f>
       </c>
       <c r="H18" s="18" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -1726,10 +1714,10 @@
         <v>54</v>
       </c>
       <c r="B19" s="20" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C19" s="20" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D19" s="21">
         <v>2</v>
@@ -1744,7 +1732,7 @@
         <f>D19*F19</f>
       </c>
       <c r="H19" s="23" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -1752,16 +1740,16 @@
         <v>54</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C20" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="D20" s="16">
+        <v>1</v>
+      </c>
+      <c r="E20" s="15" t="s">
         <v>77</v>
-      </c>
-      <c r="D20" s="16">
-        <v>2</v>
-      </c>
-      <c r="E20" s="15" t="s">
-        <v>51</v>
       </c>
       <c r="F20" s="17">
         <v>0</v>
@@ -1774,99 +1762,73 @@
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="26" t="s">
-        <v>54</v>
-      </c>
-      <c r="B21" s="20" t="s">
+      <c r="A21" s="24" t="s">
         <v>79</v>
       </c>
-      <c r="C21" s="20" t="s">
+      <c r="B21" s="24"/>
+      <c r="C21" s="24"/>
+      <c r="D21" s="24"/>
+      <c r="E21" s="24"/>
+      <c r="F21" s="24"/>
+      <c r="G21" s="25">
+        <f>SUM(G13:G20)</f>
+      </c>
+      <c r="H21" s="20"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="20"/>
+      <c r="B22" s="20"/>
+      <c r="C22" s="20"/>
+      <c r="D22" s="20"/>
+      <c r="E22" s="20"/>
+      <c r="F22" s="20"/>
+      <c r="G22" s="20"/>
+      <c r="H22" s="20"/>
+    </row>
+    <row r="23" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="28" t="s">
         <v>80</v>
       </c>
-      <c r="D21" s="21">
-        <v>1</v>
-      </c>
-      <c r="E21" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="F21" s="22">
-        <v>0</v>
-      </c>
-      <c r="G21" s="22">
-        <f>D21*F21</f>
-      </c>
-      <c r="H21" s="23" t="s">
+      <c r="B23" s="28"/>
+      <c r="C23" s="28"/>
+      <c r="D23" s="28"/>
+      <c r="E23" s="28"/>
+      <c r="F23" s="28"/>
+      <c r="G23" s="29">
+        <f>G11+G21</f>
+      </c>
+      <c r="H23" s="20"/>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" s="30" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="24" t="s">
-        <v>82</v>
-      </c>
-      <c r="B22" s="24"/>
-      <c r="C22" s="24"/>
-      <c r="D22" s="24"/>
-      <c r="E22" s="24"/>
-      <c r="F22" s="24"/>
-      <c r="G22" s="25">
-        <f>SUM(G13:G21)</f>
-      </c>
-      <c r="H22" s="20"/>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="20"/>
-      <c r="B23" s="20"/>
-      <c r="C23" s="20"/>
-      <c r="D23" s="20"/>
-      <c r="E23" s="20"/>
-      <c r="F23" s="20"/>
-      <c r="G23" s="20"/>
-      <c r="H23" s="20"/>
-    </row>
-    <row r="24" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="28" t="s">
-        <v>83</v>
-      </c>
-      <c r="B24" s="28"/>
-      <c r="C24" s="28"/>
-      <c r="D24" s="28"/>
-      <c r="E24" s="28"/>
-      <c r="F24" s="28"/>
-      <c r="G24" s="29">
-        <f>G11+G22</f>
-      </c>
-      <c r="H24" s="20"/>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" s="30" t="s">
-        <v>84</v>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>36</v>
+      </c>
+      <c r="B26" s="31">
+        <f>G11/G23</f>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="B27" s="31">
-        <f>G11/G24</f>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>54</v>
-      </c>
-      <c r="B28" s="31">
-        <f>G22/G24</f>
+        <f>G21/G23</f>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:H21"/>
+  <autoFilter ref="A5:H20"/>
   <mergeCells count="6">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="A11:F11"/>
-    <mergeCell ref="A22:F22"/>
-    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A23:F23"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -1879,7 +1841,7 @@
     <tabColor rgb="FF0EA5E9"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AH24"/>
+  <dimension ref="A1:AH23"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -1892,7 +1854,7 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1930,7 +1892,7 @@
     </row>
     <row r="2" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -1968,30 +1930,30 @@
     </row>
     <row r="3" spans="7:34" x14ac:dyDescent="0.25">
       <c r="G3" s="32" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="P3" s="32" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="D4" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="E4" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="F4" s="13" t="s">
         <v>91</v>
-      </c>
-      <c r="D4" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="E4" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="F4" s="13" t="s">
-        <v>94</v>
       </c>
       <c r="G4" s="33">
         <v>23</v>
@@ -2080,13 +2042,13 @@
     </row>
     <row r="5" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A5" s="19" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B5" s="34" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C5" s="35" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D5" s="36">
         <v>46258</v>
@@ -2128,13 +2090,13 @@
     </row>
     <row r="6" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A6" s="19" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B6" s="34" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C6" s="35" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D6" s="36">
         <v>46260</v>
@@ -2176,13 +2138,13 @@
     </row>
     <row r="7" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A7" s="19" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B7" s="34" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C7" s="35" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D7" s="36">
         <v>46266</v>
@@ -2227,16 +2189,16 @@
         <v>98</v>
       </c>
       <c r="B8" s="34" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C8" s="35" t="s">
-        <v>97</v>
+        <v>12</v>
       </c>
       <c r="D8" s="36">
-        <v>46270</v>
+        <v>46267</v>
       </c>
       <c r="E8" s="36">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="F8" s="21">
         <f>E8-D8+1</f>
@@ -2250,13 +2212,13 @@
       <c r="M8" s="20"/>
       <c r="N8" s="20"/>
       <c r="O8" s="20"/>
-      <c r="P8" s="20"/>
-      <c r="Q8" s="20"/>
-      <c r="R8" s="20"/>
-      <c r="S8" s="37"/>
-      <c r="T8" s="37"/>
-      <c r="U8" s="37"/>
-      <c r="V8" s="20"/>
+      <c r="P8" s="38"/>
+      <c r="Q8" s="38"/>
+      <c r="R8" s="38"/>
+      <c r="S8" s="38"/>
+      <c r="T8" s="38"/>
+      <c r="U8" s="38"/>
+      <c r="V8" s="38"/>
       <c r="W8" s="20"/>
       <c r="X8" s="20"/>
       <c r="Y8" s="20"/>
@@ -2272,19 +2234,19 @@
     </row>
     <row r="9" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="B9" s="34" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C9" s="35" t="s">
         <v>12</v>
       </c>
       <c r="D9" s="36">
-        <v>46267</v>
+        <v>46271</v>
       </c>
       <c r="E9" s="36">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="F9" s="21">
         <f>E9-D9+1</f>
@@ -2298,14 +2260,14 @@
       <c r="M9" s="20"/>
       <c r="N9" s="20"/>
       <c r="O9" s="20"/>
-      <c r="P9" s="38"/>
-      <c r="Q9" s="38"/>
-      <c r="R9" s="38"/>
-      <c r="S9" s="38"/>
+      <c r="P9" s="20"/>
+      <c r="Q9" s="20"/>
+      <c r="R9" s="20"/>
+      <c r="S9" s="20"/>
       <c r="T9" s="38"/>
       <c r="U9" s="38"/>
       <c r="V9" s="38"/>
-      <c r="W9" s="20"/>
+      <c r="W9" s="38"/>
       <c r="X9" s="20"/>
       <c r="Y9" s="20"/>
       <c r="Z9" s="20"/>
@@ -2320,19 +2282,19 @@
     </row>
     <row r="10" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B10" s="34" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C10" s="35" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D10" s="36">
-        <v>46271</v>
+        <v>46273</v>
       </c>
       <c r="E10" s="36">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="F10" s="21">
         <f>E10-D10+1</f>
@@ -2350,11 +2312,11 @@
       <c r="Q10" s="20"/>
       <c r="R10" s="20"/>
       <c r="S10" s="20"/>
-      <c r="T10" s="38"/>
-      <c r="U10" s="38"/>
-      <c r="V10" s="38"/>
-      <c r="W10" s="38"/>
-      <c r="X10" s="20"/>
+      <c r="T10" s="20"/>
+      <c r="U10" s="20"/>
+      <c r="V10" s="39"/>
+      <c r="W10" s="39"/>
+      <c r="X10" s="39"/>
       <c r="Y10" s="20"/>
       <c r="Z10" s="20"/>
       <c r="AA10" s="20"/>
@@ -2368,19 +2330,19 @@
     </row>
     <row r="11" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="B11" s="34" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C11" s="35" t="s">
         <v>14</v>
       </c>
       <c r="D11" s="36">
-        <v>46273</v>
+        <v>46276</v>
       </c>
       <c r="E11" s="36">
-        <v>46275</v>
+        <v>46277</v>
       </c>
       <c r="F11" s="21">
         <f>E11-D11+1</f>
@@ -2400,11 +2362,11 @@
       <c r="S11" s="20"/>
       <c r="T11" s="20"/>
       <c r="U11" s="20"/>
-      <c r="V11" s="39"/>
-      <c r="W11" s="39"/>
-      <c r="X11" s="39"/>
-      <c r="Y11" s="20"/>
-      <c r="Z11" s="20"/>
+      <c r="V11" s="20"/>
+      <c r="W11" s="20"/>
+      <c r="X11" s="20"/>
+      <c r="Y11" s="39"/>
+      <c r="Z11" s="39"/>
       <c r="AA11" s="20"/>
       <c r="AB11" s="20"/>
       <c r="AC11" s="20"/>
@@ -2416,19 +2378,19 @@
     </row>
     <row r="12" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
-        <v>98</v>
+        <v>75</v>
       </c>
       <c r="B12" s="34" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C12" s="35" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D12" s="36">
-        <v>46276</v>
+        <v>46274</v>
       </c>
       <c r="E12" s="36">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="F12" s="21">
         <f>E12-D12+1</f>
@@ -2449,11 +2411,11 @@
       <c r="T12" s="20"/>
       <c r="U12" s="20"/>
       <c r="V12" s="20"/>
-      <c r="W12" s="20"/>
-      <c r="X12" s="20"/>
-      <c r="Y12" s="39"/>
-      <c r="Z12" s="39"/>
-      <c r="AA12" s="20"/>
+      <c r="W12" s="40"/>
+      <c r="X12" s="40"/>
+      <c r="Y12" s="40"/>
+      <c r="Z12" s="40"/>
+      <c r="AA12" s="40"/>
       <c r="AB12" s="20"/>
       <c r="AC12" s="20"/>
       <c r="AD12" s="20"/>
@@ -2464,16 +2426,16 @@
     </row>
     <row r="13" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A13" s="19" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="B13" s="34" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C13" s="35" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D13" s="36">
-        <v>46274</v>
+        <v>46277</v>
       </c>
       <c r="E13" s="36">
         <v>46278</v>
@@ -2497,9 +2459,9 @@
       <c r="T13" s="20"/>
       <c r="U13" s="20"/>
       <c r="V13" s="20"/>
-      <c r="W13" s="40"/>
-      <c r="X13" s="40"/>
-      <c r="Y13" s="40"/>
+      <c r="W13" s="20"/>
+      <c r="X13" s="20"/>
+      <c r="Y13" s="20"/>
       <c r="Z13" s="40"/>
       <c r="AA13" s="40"/>
       <c r="AB13" s="20"/>
@@ -2512,16 +2474,16 @@
     </row>
     <row r="14" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A14" s="19" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B14" s="34" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C14" s="35" t="s">
-        <v>14</v>
+        <v>94</v>
       </c>
       <c r="D14" s="36">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="E14" s="36">
         <v>46278</v>
@@ -2548,7 +2510,7 @@
       <c r="W14" s="20"/>
       <c r="X14" s="20"/>
       <c r="Y14" s="20"/>
-      <c r="Z14" s="40"/>
+      <c r="Z14" s="20"/>
       <c r="AA14" s="40"/>
       <c r="AB14" s="20"/>
       <c r="AC14" s="20"/>
@@ -2560,19 +2522,19 @@
     </row>
     <row r="15" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="B15" s="34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C15" s="35" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D15" s="36">
         <v>46278</v>
       </c>
       <c r="E15" s="36">
-        <v>46278</v>
+        <v>46285</v>
       </c>
       <c r="F15" s="21">
         <f>E15-D15+1</f>
@@ -2597,27 +2559,27 @@
       <c r="X15" s="20"/>
       <c r="Y15" s="20"/>
       <c r="Z15" s="20"/>
-      <c r="AA15" s="40"/>
-      <c r="AB15" s="20"/>
-      <c r="AC15" s="20"/>
-      <c r="AD15" s="20"/>
-      <c r="AE15" s="20"/>
-      <c r="AF15" s="20"/>
-      <c r="AG15" s="20"/>
-      <c r="AH15" s="20"/>
+      <c r="AA15" s="41"/>
+      <c r="AB15" s="41"/>
+      <c r="AC15" s="41"/>
+      <c r="AD15" s="41"/>
+      <c r="AE15" s="41"/>
+      <c r="AF15" s="41"/>
+      <c r="AG15" s="41"/>
+      <c r="AH15" s="41"/>
     </row>
     <row r="16" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="B16" s="34" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C16" s="35" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D16" s="36">
-        <v>46278</v>
+        <v>46283</v>
       </c>
       <c r="E16" s="36">
         <v>46285</v>
@@ -2645,96 +2607,48 @@
       <c r="X16" s="20"/>
       <c r="Y16" s="20"/>
       <c r="Z16" s="20"/>
-      <c r="AA16" s="41"/>
-      <c r="AB16" s="41"/>
-      <c r="AC16" s="41"/>
-      <c r="AD16" s="41"/>
-      <c r="AE16" s="41"/>
+      <c r="AA16" s="20"/>
+      <c r="AB16" s="20"/>
+      <c r="AC16" s="20"/>
+      <c r="AD16" s="20"/>
+      <c r="AE16" s="20"/>
       <c r="AF16" s="41"/>
       <c r="AG16" s="41"/>
       <c r="AH16" s="41"/>
     </row>
-    <row r="17" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A17" s="19" t="s">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" s="30" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="42"/>
+      <c r="B19" s="43" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="44"/>
+      <c r="B20" s="43" t="s">
         <v>98</v>
       </c>
-      <c r="B17" s="34" t="s">
-        <v>113</v>
-      </c>
-      <c r="C17" s="35" t="s">
-        <v>97</v>
-      </c>
-      <c r="D17" s="36">
-        <v>46283</v>
-      </c>
-      <c r="E17" s="36">
-        <v>46285</v>
-      </c>
-      <c r="F17" s="21">
-        <f>E17-D17+1</f>
-      </c>
-      <c r="G17" s="20"/>
-      <c r="H17" s="20"/>
-      <c r="I17" s="20"/>
-      <c r="J17" s="20"/>
-      <c r="K17" s="20"/>
-      <c r="L17" s="20"/>
-      <c r="M17" s="20"/>
-      <c r="N17" s="20"/>
-      <c r="O17" s="20"/>
-      <c r="P17" s="20"/>
-      <c r="Q17" s="20"/>
-      <c r="R17" s="20"/>
-      <c r="S17" s="20"/>
-      <c r="T17" s="20"/>
-      <c r="U17" s="20"/>
-      <c r="V17" s="20"/>
-      <c r="W17" s="20"/>
-      <c r="X17" s="20"/>
-      <c r="Y17" s="20"/>
-      <c r="Z17" s="20"/>
-      <c r="AA17" s="20"/>
-      <c r="AB17" s="20"/>
-      <c r="AC17" s="20"/>
-      <c r="AD17" s="20"/>
-      <c r="AE17" s="20"/>
-      <c r="AF17" s="41"/>
-      <c r="AG17" s="41"/>
-      <c r="AH17" s="41"/>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="30" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="42"/>
-      <c r="B20" s="43" t="s">
-        <v>95</v>
-      </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="44"/>
+      <c r="A21" s="45"/>
       <c r="B21" s="43" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="45"/>
+      <c r="A22" s="46"/>
       <c r="B22" s="43" t="s">
-        <v>105</v>
+        <v>75</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="46"/>
+      <c r="A23" s="47"/>
       <c r="B23" s="43" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="47"/>
-      <c r="B24" s="43" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -2765,7 +2679,7 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2775,7 +2689,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -2785,7 +2699,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="B3" s="12"/>
       <c r="C3" s="12"/>
@@ -2795,30 +2709,30 @@
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="E5" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="F5" s="13" t="s">
         <v>119</v>
-      </c>
-      <c r="C5" s="13" t="s">
-        <v>120</v>
-      </c>
-      <c r="D5" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="E5" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="F5" s="13" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="48" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="C6" s="16">
         <v>400</v>
@@ -2830,15 +2744,15 @@
         <f>IFERROR(D6/C6,0)</f>
       </c>
       <c r="F6" s="50" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="51" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C7" s="21">
         <v>150</v>
@@ -2850,15 +2764,15 @@
         <f>IFERROR(D7/C7,0)</f>
       </c>
       <c r="F7" s="35" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="48" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="C8" s="16">
         <v>600</v>
@@ -2870,13 +2784,13 @@
         <f>IFERROR(D8/C8,0)</f>
       </c>
       <c r="F8" s="50" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="20"/>
       <c r="B9" s="53" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C9" s="54">
         <f>SUM(C6:C8)</f>
@@ -2899,10 +2813,10 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="51" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="B11" s="20" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C11" s="21">
         <v>300</v>
@@ -2914,15 +2828,15 @@
         <f>IFERROR(D11/C11,0)</f>
       </c>
       <c r="F11" s="35" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="48" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C12" s="16">
         <v>120</v>
@@ -2934,15 +2848,15 @@
         <f>IFERROR(D12/C12,0)</f>
       </c>
       <c r="F12" s="50" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="51" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B13" s="20" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C13" s="21">
         <v>90</v>
@@ -2954,13 +2868,13 @@
         <f>IFERROR(D13/C13,0)</f>
       </c>
       <c r="F13" s="35" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="20"/>
       <c r="B14" s="53" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C14" s="54">
         <f>SUM(C11:C13)</f>
@@ -2983,10 +2897,10 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="48" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C16" s="16">
         <v>40</v>
@@ -2998,15 +2912,15 @@
         <f>IFERROR(D16/C16,0)</f>
       </c>
       <c r="F16" s="50" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="51" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B17" s="20" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C17" s="21">
         <v>25</v>
@@ -3018,15 +2932,15 @@
         <f>IFERROR(D17/C17,0)</f>
       </c>
       <c r="F17" s="35" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="48" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C18" s="16">
         <v>60</v>
@@ -3038,13 +2952,13 @@
         <f>IFERROR(D18/C18,0)</f>
       </c>
       <c r="F18" s="50" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="20"/>
       <c r="B19" s="53" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="C19" s="54">
         <f>SUM(C16:C18)</f>
@@ -3059,7 +2973,7 @@
     </row>
     <row r="22" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -3069,7 +2983,7 @@
     </row>
     <row r="23" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -3079,30 +2993,30 @@
     </row>
     <row r="25" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="13" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="B25" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="C25" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="D25" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="E25" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="F25" s="13" t="s">
         <v>146</v>
-      </c>
-      <c r="C25" s="13" t="s">
-        <v>147</v>
-      </c>
-      <c r="D25" s="13" t="s">
-        <v>148</v>
-      </c>
-      <c r="E25" s="13" t="s">
-        <v>149</v>
-      </c>
-      <c r="F25" s="13" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="56" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B26" s="35" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="C26" s="21">
         <f>D9</f>
@@ -3114,15 +3028,15 @@
         <f>C26*D26</f>
       </c>
       <c r="F26" s="35" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="56" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="B27" s="35" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="C27" s="21">
         <f>D14</f>
@@ -3134,15 +3048,15 @@
         <f>C27*D27</f>
       </c>
       <c r="F27" s="35" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="56" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B28" s="35" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C28" s="21">
         <f>D19</f>
@@ -3154,13 +3068,13 @@
         <f>C28*D28</f>
       </c>
       <c r="F28" s="35" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="20"/>
       <c r="B29" s="58" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C29" s="20"/>
       <c r="D29" s="20"/>
@@ -3180,20 +3094,20 @@
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="20"/>
       <c r="B31" s="58" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C31" s="20"/>
       <c r="D31" s="20"/>
       <c r="E31" s="60">
-        <f>'1. Presupuesto'!G24</f>
+        <f>'1. Presupuesto'!G23</f>
       </c>
       <c r="F31" s="61" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
     </row>
     <row r="33" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="62" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="B33" s="62"/>
       <c r="C33" s="62"/>
@@ -3202,12 +3116,12 @@
         <f>IFERROR(E29/E31*1000,0)</f>
       </c>
       <c r="F33" s="64" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -3217,7 +3131,7 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="12" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="B36" s="12"/>
       <c r="C36" s="12"/>
